--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/DELAWARE_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/DELAWARE_2020.xlsx
@@ -1464,7 +1464,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>San Simon De Guerero</t>
+          <t>San Simon De Guerrero</t>
         </is>
       </c>
       <c r="C62">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C77">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Ayotoxco De Guerero</t>
+          <t>Ayotoxco De Guerrero</t>
         </is>
       </c>
       <c r="C201">
